--- a/artfynd/A 11979-2026 artfynd.xlsx
+++ b/artfynd/A 11979-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127618184</v>
+        <v>15098512</v>
       </c>
       <c r="B2" t="n">
-        <v>56599</v>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208257</v>
+        <v>100679</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Brun gräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Coenonympha hero</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Koltorget, Dlr</t>
+          <t>Källslätten parkeringen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525952</v>
+        <v>525977</v>
       </c>
       <c r="R2" t="n">
-        <v>6721826</v>
+        <v>6721738</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Vid de höga örterna på N sidan skogsbilvägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,26 +775,35 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Falu kommun inventering ansvarsarter</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127618351</v>
+        <v>126088163</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +811,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,13 +844,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525956</v>
+        <v>526004</v>
       </c>
       <c r="R3" t="n">
-        <v>6721879</v>
+        <v>6721729</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +874,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,15 +904,944 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Uno Skog, Freja Skog, Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126088320</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Koltorget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>526004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6721729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Uno Skog, Freja Skog</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86201416</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Koltorget, P-plats Källslätten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526025</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6721721</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Urban Grenmyr</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Urban Grenmyr</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127618351</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koltorget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>525956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6721879</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Håkan Thenander</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86201418</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Koltorget, P-plats Källslätten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>526025</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6721721</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Urban Grenmyr</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Urban Grenmyr</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126090562</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Koltorget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>526004</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6721729</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Skog, Freja Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>15098513</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källslätten parkeringen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>525977</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6721738</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-07-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vid de höga örterna på N sidan skogsbilvägen.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Falu kommun inventering ansvarsarter</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16002319</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>slag-/vattenhåvning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Koltorget, Källslätten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>525992</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-06-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blomrik vägkant vid skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127618184</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Koltorget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>525952</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6721826</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
